--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.33032102479183</v>
+        <v>4.766177166528673</v>
       </c>
       <c r="D2" t="n">
-        <v>12.34829302289684</v>
+        <v>2.006597616220736</v>
       </c>
       <c r="E2" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.81129990365521</v>
+        <v>2.569336234343971</v>
       </c>
       <c r="D3" t="n">
-        <v>14.24934977889575</v>
+        <v>2.31551933907056</v>
       </c>
       <c r="E3" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F3" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.8206251040849</v>
+        <v>6.145851579413796</v>
       </c>
       <c r="D4" t="n">
-        <v>37.65113083935419</v>
+        <v>6.118308761395056</v>
       </c>
       <c r="E4" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F4" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.23264519098347</v>
+        <v>4.912804843534814</v>
       </c>
       <c r="D5" t="n">
-        <v>30.0288300034325</v>
+        <v>4.879684875557781</v>
       </c>
       <c r="E5" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F5" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.71437332114384</v>
+        <v>6.778585664685874</v>
       </c>
       <c r="D6" t="n">
-        <v>30.38558787677612</v>
+        <v>4.93765802997612</v>
       </c>
       <c r="E6" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F6" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.17177375576858</v>
+        <v>7.502913235312394</v>
       </c>
       <c r="D7" t="n">
-        <v>17.26426568622306</v>
+        <v>2.805443174011248</v>
       </c>
       <c r="E7" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F7" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.7215599589625</v>
+        <v>5.317253493331407</v>
       </c>
       <c r="D8" t="n">
-        <v>32.64879777782657</v>
+        <v>5.305429638896818</v>
       </c>
       <c r="E8" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F8" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.65583977509816</v>
+        <v>4.006573963453451</v>
       </c>
       <c r="D9" t="n">
-        <v>24.76075796107891</v>
+        <v>4.023623168675323</v>
       </c>
       <c r="E9" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F9" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.78284492784853</v>
+        <v>6.139712300775386</v>
       </c>
       <c r="D10" t="n">
-        <v>37.9306149924318</v>
+        <v>6.163724936270167</v>
       </c>
       <c r="E10" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F10" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.66391714250883</v>
+        <v>7.907886535657685</v>
       </c>
       <c r="D11" t="n">
-        <v>48.72449464208842</v>
+        <v>7.917730379339369</v>
       </c>
       <c r="E11" t="n">
-        <v>9.512993774935795</v>
+        <v>1.545861488427067</v>
       </c>
       <c r="F11" t="n">
-        <v>10.99499458843145</v>
+        <v>1.78668662062011</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
